--- a/data_extactor/batch/101_150.xlsx
+++ b/data_extactor/batch/101_150.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A54AAF-34DC-45C6-8972-346C016F52C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7055FA6-8BC1-4146-8540-AAB9CCF46E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="535">
   <si>
     <t>13-2053.00</t>
   </si>
@@ -1519,6 +1519,117 @@
   </si>
   <si>
     <t>Analyze data on conditions such as site location, drainage, or structure location for environmental reports or landscaping plans. | Collaborate with architects or related professionals on whole building design to maximize the aesthetic features of structures or surrounding land and to improve energy efficiency. | Collaborate with estimators to cost projects, create project plans, or coordinate bids from landscaping contractors. | Confer with clients, engineering personnel, or architects on landscape projects. | Create landscapes that minimize water consumption such as by incorporating drought-resistant grasses or indigenous plants. | Design and integrate rainwater harvesting or gray and reclaimed water systems to conserve water into building or land designs. | Develop marketing materials, proposals, or presentations to generate new work opportunities. | Develop planting plans to help clients garden productively or to achieve particular aesthetic effects. | Identify and select appropriate sustainable materials for use in landscape designs, such as recycled wood or recycled concrete boards for structural elements or recycled tires for playground bedding. | Inspect landscape work to ensure compliance with specifications, evaluate quality of materials or work, or advise clients or construction personnel. | Inspect proposed sites to identify structural elements of land areas or other important site information, such as soil condition, existing landscaping, or the proximity of water management facilities. | Integrate existing land features or landscaping into designs. | Manage the work of subcontractors to ensure quality control. | Prepare conceptual drawings, graphics, or other visual representations of land areas to show predicted growth or development of land areas over time. | Prepare graphic representations or drawings of proposed plans or designs. | Prepare site plans, specifications, or cost estimates for land development. | Present project plans or designs to public stakeholders, such as government agencies or community groups. | Provide follow-up consultations for clients to ensure landscape designs are maturing or developing as planned. | Research latest products, technology, or design trends to stay current in the field.</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Mathematics | Active Learning | Writing | Speaking | Active Listening | Science | Monitoring</t>
+  </si>
+  <si>
+    <t>Economics and Accounting | Mathematics | English Language | Computers and Electronics | Administration and Management | Law and Government | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization | Mathematical Reasoning | Number Facility | Perceptual Speed | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Level of Competition</t>
+  </si>
+  <si>
+    <t>Financial Analyst | Financial Consultant | Financial Operations Specialist | Financial Planning Analyst | Financial Specialist | Investment Analyst | Portfolio Analyst | Risk Analyst | Securities Analyst | Treasury Analyst</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Structured query language SQL | Python | R | SAS | IBM SPSS Statistics | Tableau | Microsoft Power BI | Minitab | The MathWorks MATLAB | Oracle Database | Microsoft Access | Database software | Microsoft Word | Email software | Microsoft PowerPoint | Microsoft Outlook | Microsoft Office software | Microsoft SharePoint | Web browser software | Google Docs | Calendar management software | Spreadsheet programs | Adobe Acrobat</t>
+  </si>
+  <si>
+    <t>Economics and Accounting | Mathematics | English Language | Administration and Management | Computers and Electronics | Law and Government | Customer and Personal Service | Sales and Marketing | Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Level of Competition | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Financial Quantitative Analysts | Fraud Examiners, Investigators and Analysts | Financial and Investment Analysts | Personal Financial Advisors | Financial Risk Specialists | Budget Analysts | Credit Analysts | Insurance Underwriters | Financial Examiners | Credit Counselors | Loan Officers | Tax Examiners and Collectors, and Revenue Agents | Tax Preparers | Accountants and Auditors | Appraisers and Assessors of Real Estate | Appraisers of Personal and Business Property | Financial Managers | Treasurers and Controllers | Investment Fund Managers | Management Analysts</t>
+  </si>
+  <si>
+    <t>Perform financial analysis and advisory duties not classified separately. | Analyze financial statements, market data, and economic indicators to support decisions. | Build and maintain financial models, forecasts, and valuation analyses. | Prepare reports and recommendations on investments, financing, and risk exposure. | Monitor portfolio performance and recommend adjustments to holdings or strategy. | Evaluate the creditworthiness and financial condition of individuals or organizations. | Ensure compliance with financial regulations, reporting standards, and internal controls. | Reconcile accounts and investigate discrepancies in financial records. | Advise clients or management on financial products, tax implications, and planning options. | Conduct due diligence on transactions, counterparties, and financial instruments. | Prepare budgets and variance analyses for business units or clients. | Document methodologies, assumptions, and findings for audit and review purposes. | Present financial findings to management, clients, and regulatory bodies. | Track regulatory and market developments affecting financial positions.</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Monitoring | Active Listening | Speaking | Mathematics | Active Learning | Writing | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Design | English Language | Communications and Media | Customer and Personal Service | Mathematics | Fine Arts | Sales and Marketing | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization | Mathematical Reasoning | Number Facility | Perceptual Speed | Flexibility of Closure | Visual Color Discrimination</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Level of Competition | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Automation Engineer | Cloud Engineer | Computer Specialist | DevOps Engineer | Information Technology Consultant | Information Technology Specialist | Platform Engineer | Site Reliability Engineer | Systems Engineer | Technical Specialist</t>
+  </si>
+  <si>
+    <t>Structured query language SQL | Python | Oracle Database | Microsoft Access | Atlassian JIRA | Atlassian Confluence | Slack | Microsoft SharePoint | Web browser software | Database software | Microsoft Excel | Microsoft Word | Microsoft Windows | Email software | Microsoft Power BI | Microsoft Office software | Microsoft Outlook</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | English Language | Mathematics | Engineering and Technology | Telecommunications | Administration and Management | Customer and Personal Service | Education and Training | Design</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Degree of Automation | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Web Administrators | Geographic Information Systems Technologists and Technicians | Document Management Specialists | Penetration Testers | Information Security Engineers | Digital Forensics Analysts | Blockchain Engineers | Computer Systems Engineers/Architects | Information Technology Project Managers | Computer Systems Analysts | Information Security Analysts | Computer Network Architects | Network and Computer Systems Administrators | Database Administrators | Database Architects | Software Developers | Computer Programmers | Web Developers | Computer Network Support Specialists | Computer and Information Systems Managers</t>
+  </si>
+  <si>
+    <t>Perform computer and information technology duties not classified separately. | Design, configure, deploy, and maintain computing systems, platforms, and services. | Automate build, deployment, monitoring, and recovery processes. | Diagnose and resolve hardware, software, network, and integration problems. | Evaluate new technologies and recommend adoption based on requirements and cost. | Develop and maintain scripts, tools, and utilities supporting technical operations. | Implement security controls, access policies, and data protection measures. | Monitor system performance, capacity, and availability and tune configurations. | Document system architectures, configurations, and operating procedures. | Coordinate with developers, analysts, and vendors to deliver technical solutions. | Plan and execute system migrations, upgrades, and disaster recovery testing. | Provide technical guidance and training to users and junior staff. | Analyze requirements and translate them into technical specifications. | Maintain inventories of hardware, software licenses, and configuration records.</t>
+  </si>
+  <si>
+    <t>Application Security Engineer | Ethical Hacker | Offensive Security Engineer | Penetration Tester | Red Team Operator | Security Assessor | Security Consultant | Vulnerability Assessment Analyst | Vulnerability Researcher | White Hat Hacker</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Telecommunications | English Language | Mathematics | Engineering and Technology | Law and Government | Public Safety and Security | Administration and Management</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Coordinate or Lead Others in Accomplishing Work Activities | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Computer Forensics Analyst | Cyber Forensics Investigator | Digital Evidence Analyst | Digital Forensics Analyst | Digital Forensics Examiner | Forensic Computer Examiner | Incident Response Analyst | Malware Analyst | Cybercrime Investigator | Forensic Data Analyst</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Law and Government | English Language | Telecommunications | Public Safety and Security | Mathematics | Engineering and Technology | Administration and Management</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Consequence of Error | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Blockchain Architect | Blockchain Developer | Blockchain Engineer | Cryptocurrency Engineer | Distributed Ledger Developer | Distributed Systems Engineer | Smart Contract Developer | Smart Contract Engineer | Web3 Developer | Protocol Engineer</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Mathematics | English Language | Engineering and Technology | Telecommunications | Economics and Accounting | Administration and Management | Design</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Coordinate or Lead Others in Accomplishing Work Activities | Degree of Automation</t>
+  </si>
+  <si>
+    <t>Applied Scientist | Data Analyst | Data Science Specialist | Data Scientist | Machine Learning Engineer | Machine Learning Scientist | Quantitative Researcher | Research Data Scientist | Statistical Modeler | Analytics Scientist</t>
+  </si>
+  <si>
+    <t>Mathematics | Computers and Electronics | English Language | Engineering and Technology | Administration and Management | Economics and Accounting | Education and Training | Communications and Media</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Applied Mathematician | Applied Statistician | Computational Scientist | Cryptanalyst | Decision Scientist | Mathematical Modeler | Mathematical Statistician | Numerical Analyst | Optimization Analyst | Quantitative Analyst</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Structured query language SQL | Python | R | SAS | IBM SPSS Statistics | Tableau | Microsoft Power BI | Minitab | The MathWorks MATLAB | Oracle Database | Microsoft Access | Database software | Microsoft Word | Email software | Microsoft PowerPoint | Web browser software</t>
+  </si>
+  <si>
+    <t>Mathematics | Computers and Electronics | English Language | Physics | Engineering and Technology | Economics and Accounting | Education and Training | Administration and Management</t>
+  </si>
+  <si>
+    <t>Bioinformatics Technicians | Actuaries | Mathematicians | Operations Research Analysts | Statisticians | Biostatisticians | Data Scientists | Business Intelligence Analysts | Clinical Data Managers | Financial Quantitative Analysts | Computer and Information Research Scientists | Computer Programmers | Software Developers | Database Architects | Economists | Financial and Investment Analysts | Market Research Analysts and Marketing Specialists | Natural Sciences Managers | Physicists | Mathematical Science Teachers, Postsecondary</t>
+  </si>
+  <si>
+    <t>Perform mathematical and statistical science duties not classified separately. | Develop mathematical models to describe, analyze, and predict complex systems. | Apply numerical, statistical, and optimization methods to solve applied problems. | Design experiments and sampling plans and determine appropriate analytical methods. | Write, test, and document programs implementing mathematical algorithms. | Analyze large datasets to identify patterns, relationships, and anomalies. | Validate models against empirical data and quantify uncertainty in results. | Prepare technical reports, papers, and presentations describing methods and findings. | Consult with scientists, engineers, and managers to define analytical requirements. | Review literature and evaluate new mathematical techniques for applicability. | Develop decision support tools and simulations for planning and forecasting. | Verify the accuracy and reproducibility of computational results. | Advise on the interpretation and limitations of quantitative findings. | Maintain documentation of data sources, assumptions, and model versions.</t>
   </si>
 </sst>
 </file>
@@ -1887,6 +1998,18 @@
       <c r="D2" t="s">
         <v>14</v>
       </c>
+      <c r="E2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F2" t="s">
+        <v>499</v>
+      </c>
+      <c r="G2" t="s">
+        <v>500</v>
+      </c>
+      <c r="H2" t="s">
+        <v>501</v>
+      </c>
       <c r="I2" t="s">
         <v>15</v>
       </c>
@@ -2079,8 +2202,32 @@
       <c r="B8" t="s">
         <v>74</v>
       </c>
+      <c r="C8" t="s">
+        <v>502</v>
+      </c>
+      <c r="D8" t="s">
+        <v>503</v>
+      </c>
+      <c r="E8" t="s">
+        <v>498</v>
+      </c>
+      <c r="F8" t="s">
+        <v>504</v>
+      </c>
+      <c r="G8" t="s">
+        <v>500</v>
+      </c>
+      <c r="H8" t="s">
+        <v>505</v>
+      </c>
+      <c r="I8" t="s">
+        <v>506</v>
+      </c>
       <c r="J8" t="s">
         <v>75</v>
+      </c>
+      <c r="K8" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -2726,6 +2873,18 @@
       <c r="D27" t="s">
         <v>277</v>
       </c>
+      <c r="E27" t="s">
+        <v>508</v>
+      </c>
+      <c r="F27" t="s">
+        <v>509</v>
+      </c>
+      <c r="G27" t="s">
+        <v>510</v>
+      </c>
+      <c r="H27" t="s">
+        <v>511</v>
+      </c>
       <c r="I27" t="s">
         <v>278</v>
       </c>
@@ -2778,8 +2937,32 @@
       <c r="B29" t="s">
         <v>293</v>
       </c>
+      <c r="C29" t="s">
+        <v>512</v>
+      </c>
+      <c r="D29" t="s">
+        <v>513</v>
+      </c>
+      <c r="E29" t="s">
+        <v>508</v>
+      </c>
+      <c r="F29" t="s">
+        <v>514</v>
+      </c>
+      <c r="G29" t="s">
+        <v>500</v>
+      </c>
+      <c r="H29" t="s">
+        <v>515</v>
+      </c>
+      <c r="I29" t="s">
+        <v>516</v>
+      </c>
       <c r="J29" t="s">
         <v>294</v>
+      </c>
+      <c r="K29" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
@@ -2894,8 +3077,23 @@
       <c r="B33" t="s">
         <v>329</v>
       </c>
+      <c r="C33" t="s">
+        <v>518</v>
+      </c>
       <c r="D33" t="s">
         <v>330</v>
+      </c>
+      <c r="E33" t="s">
+        <v>508</v>
+      </c>
+      <c r="F33" t="s">
+        <v>519</v>
+      </c>
+      <c r="G33" t="s">
+        <v>500</v>
+      </c>
+      <c r="H33" t="s">
+        <v>520</v>
       </c>
       <c r="I33" t="s">
         <v>331</v>
@@ -2949,8 +3147,23 @@
       <c r="B35" t="s">
         <v>346</v>
       </c>
+      <c r="C35" t="s">
+        <v>521</v>
+      </c>
       <c r="D35" t="s">
         <v>347</v>
+      </c>
+      <c r="E35" t="s">
+        <v>508</v>
+      </c>
+      <c r="F35" t="s">
+        <v>522</v>
+      </c>
+      <c r="G35" t="s">
+        <v>500</v>
+      </c>
+      <c r="H35" t="s">
+        <v>523</v>
       </c>
       <c r="I35" t="s">
         <v>348</v>
@@ -2969,8 +3182,23 @@
       <c r="B36" t="s">
         <v>352</v>
       </c>
+      <c r="C36" t="s">
+        <v>524</v>
+      </c>
       <c r="D36" t="s">
         <v>353</v>
+      </c>
+      <c r="E36" t="s">
+        <v>508</v>
+      </c>
+      <c r="F36" t="s">
+        <v>525</v>
+      </c>
+      <c r="G36" t="s">
+        <v>500</v>
+      </c>
+      <c r="H36" t="s">
+        <v>526</v>
       </c>
       <c r="I36" t="s">
         <v>354</v>
@@ -3234,8 +3462,23 @@
       <c r="B44" t="s">
         <v>435</v>
       </c>
+      <c r="C44" t="s">
+        <v>527</v>
+      </c>
       <c r="D44" t="s">
         <v>436</v>
+      </c>
+      <c r="E44" t="s">
+        <v>498</v>
+      </c>
+      <c r="F44" t="s">
+        <v>528</v>
+      </c>
+      <c r="G44" t="s">
+        <v>500</v>
+      </c>
+      <c r="H44" t="s">
+        <v>529</v>
       </c>
       <c r="I44" t="s">
         <v>437</v>
@@ -3324,8 +3567,32 @@
       <c r="B47" t="s">
         <v>463</v>
       </c>
+      <c r="C47" t="s">
+        <v>530</v>
+      </c>
+      <c r="D47" t="s">
+        <v>531</v>
+      </c>
+      <c r="E47" t="s">
+        <v>498</v>
+      </c>
+      <c r="F47" t="s">
+        <v>532</v>
+      </c>
+      <c r="G47" t="s">
+        <v>500</v>
+      </c>
+      <c r="H47" t="s">
+        <v>529</v>
+      </c>
+      <c r="I47" t="s">
+        <v>533</v>
+      </c>
       <c r="J47" t="s">
         <v>464</v>
+      </c>
+      <c r="K47" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
